--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="510" yWindow="1230" windowWidth="21600" windowHeight="11295" tabRatio="899" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV ANDROMEDA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV AQUARIUS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV AQUILA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV CENTAURUS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV CEPHEUS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV CIRCINUS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV CYGNUS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV DELPHINUS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV DRACO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV HYDRA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV LIBRA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV PERSEUS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV PHOENIX" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV REGULUS" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV TAURUS" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV URSUS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STARNAV VOLANS" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="STARNAV ANDROMEDA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="STARNAV AQUARIUS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="STARNAV AQUILA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="STARNAV CENTAURUS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="STARNAV CEPHEUS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="STARNAV CIRCINUS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="STARNAV CYGNUS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="STARNAV DELPHINUS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="STARNAV DRACO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="STARNAV HYDRA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="STARNAV LIBRA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="STARNAV PERSEUS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="STARNAV PHOENIX" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="STARNAV REGULUS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="STARNAV TAURUS" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="STARNAV URSUS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="STARNAV VOLANS" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STARNAV ANDROMEDA'!$A$1:$S$17</definedName>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -1046,9 +1046,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.854778</v>
       </c>
@@ -1058,12 +1055,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32152777778</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.888233</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.215214</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85416666666</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.28515625" customWidth="1" min="1" max="1"/>
@@ -1666,9 +1679,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-21.962212</v>
       </c>
@@ -1678,12 +1688,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.30833333333</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-21.967825</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-39.826687</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85347222222</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2283,9 +2309,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.887428</v>
       </c>
@@ -2295,12 +2318,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32152777778</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.861006</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.178879</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85625</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.85546875" customWidth="1" min="1" max="1"/>
@@ -2952,9 +2991,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-23.333735</v>
       </c>
@@ -2964,12 +3000,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.30902777778</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.862795</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.167763</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85694444444</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.85546875" customWidth="1" min="1" max="1"/>
@@ -3570,9 +3622,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.838448</v>
       </c>
@@ -3582,12 +3631,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32152777778</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-23.199171</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.060268</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46275.84583333333</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4236,9 +4301,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.86203</v>
       </c>
@@ -4248,10 +4310,26 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32222222222</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.862747</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.172367</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85694444444</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4268,7 +4346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -4852,9 +4930,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.857306</v>
       </c>
@@ -4864,12 +4939,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32222222222</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-24.740973</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.514408</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.14513888889</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5518,9 +5609,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-26.856745</v>
       </c>
@@ -5530,10 +5618,26 @@
       <c r="Q23" s="10" t="n">
         <v>46120.32569444444</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-26.856745</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-48.721401</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -5550,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -6135,9 +6239,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.838087</v>
       </c>
@@ -6147,12 +6248,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.31875</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85833333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.862825</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.161587</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85694444444</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.85546875" customWidth="1" min="1" max="1"/>
@@ -6754,9 +6871,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.895683</v>
       </c>
@@ -6766,12 +6880,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.31666666667</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-24.70982</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.413784</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.55</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.28515625" customWidth="1" min="1" max="1"/>
@@ -7405,9 +7535,6 @@
       <c r="A24" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B24" t="n">
-        <v/>
-      </c>
       <c r="M24" t="n">
         <v>-22.464121</v>
       </c>
@@ -7417,10 +7544,26 @@
       <c r="Q24" s="10" t="n">
         <v>46237.31736111111</v>
       </c>
-      <c r="R24" t="n">
-        <v/>
-      </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.560759</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-40.12278</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46276.90902777778</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -7438,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -8024,9 +8167,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-24.568388</v>
       </c>
@@ -8036,12 +8176,28 @@
       <c r="Q23" s="10" t="n">
         <v>46236.91458333333</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.841331</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.134846</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.85208333333</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
@@ -8641,9 +8797,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.445057</v>
       </c>
@@ -8653,10 +8806,26 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32430555556</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.375</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.410228</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.71805555555</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -8673,7 +8842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9277,9 +9446,6 @@
       <c r="A24" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B24" t="n">
-        <v/>
-      </c>
       <c r="M24" t="n">
         <v>-21.855021</v>
       </c>
@@ -9289,12 +9455,28 @@
       <c r="Q24" s="10" t="n">
         <v>46237.32569444444</v>
       </c>
-      <c r="R24" t="n">
-        <v/>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-24.543678</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-42.20084</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46278.67222222222</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5703125" customWidth="1" min="1" max="1"/>
@@ -9899,9 +10081,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.197227</v>
       </c>
@@ -9911,12 +10090,28 @@
       <c r="Q23" s="10" t="n">
         <v>46237.32430555556</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-21.940434</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-39.786179</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46277.70416666667</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -9931,7 +10126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10519,9 +10714,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.710012</v>
       </c>
@@ -10531,10 +10723,26 @@
       <c r="Q23" s="10" t="n">
         <v>46237.31944444445</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.798719</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.763451</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.58263888889</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -10551,7 +10759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" min="17" max="17"/>
@@ -11136,9 +11344,6 @@
       <c r="A23" s="10" t="n">
         <v>46237.32638888889</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.634569</v>
       </c>
@@ -11148,10 +11353,26 @@
       <c r="Q23" s="10" t="n">
         <v>46236.53194444445</v>
       </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278.85763888889</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.9534</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.726486</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46278.32291666666</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>

--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -1080,6 +1080,25 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.888254</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.215214</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.73958333334</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1092,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.28515625" customWidth="1" min="1" max="1"/>
@@ -1708,6 +1727,25 @@
         <v>46278.85347222222</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-21.92164</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-39.766262</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.41458333333</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -1724,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2338,6 +2376,25 @@
         <v>46278.85625</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.861639</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.178696</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.73611111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -2354,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.85546875" customWidth="1" min="1" max="1"/>
@@ -3020,6 +3077,25 @@
         <v>46278.85694444444</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.863752</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.167759</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -3037,7 +3113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.85546875" customWidth="1" min="1" max="1"/>
@@ -3653,6 +3729,25 @@
       <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.862938</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.161163</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.74236111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4330,6 +4425,25 @@
         <v>46278.85694444444</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.863291</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.172325</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.74236111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4346,7 +4460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -4959,6 +5073,25 @@
         <v>46278.14513888889</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-24.740973</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-42.514408</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46278.14513888889</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -4975,7 +5108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5638,6 +5771,25 @@
         <v>46120.32569444444</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-26.856745</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-48.721401</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -5654,7 +5806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -6270,6 +6422,25 @@
       <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74513888889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.89101</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.21386</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.85546875" customWidth="1" min="1" max="1"/>
@@ -6900,6 +7071,25 @@
         <v>46278.55</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-24.70982</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-42.413784</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46278.55</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -6916,7 +7106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.28515625" customWidth="1" min="1" max="1"/>
@@ -7564,6 +7754,25 @@
         <v>46276.90902777778</v>
       </c>
       <c r="S25" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.560759</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-40.12278</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <v>46276.90902777778</v>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -7581,7 +7790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -8198,6 +8407,25 @@
       <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.881721</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.117714</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.74097222222</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
@@ -8826,6 +9054,25 @@
         <v>46278.71805555555</v>
       </c>
       <c r="S24" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.439684</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-40.424923</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.45208333333</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -8842,7 +9089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9477,6 +9724,25 @@
       <c r="S25" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-21.957027</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-40.820152</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <v>46279.73819444444</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5703125" customWidth="1" min="1" max="1"/>
@@ -10115,6 +10381,25 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-21.906334</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-39.735188</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.41597222222</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10126,7 +10411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10748,6 +11033,25 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.716267</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-40.678406</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46279.34444444445</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10759,7 +11063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" min="17" max="17"/>
@@ -11378,6 +11682,25 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279.74305555555</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.9534</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-40.726486</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>46278.32291666666</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
